--- a/Output/OBC Andolan/extracted_links_OBC Andolan_failed_links.xlsx
+++ b/Output/OBC Andolan/extracted_links_OBC Andolan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A84"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,7 +438,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/congress-presses-fadnavis-govt-on-hyderabad-gazette-implementation-will-backward-classes-get-42-reservation-3713458</t>
+          <t>http://www.msn.com/en-in/news/India/what-is-the-hyderabad-gazette-giving-kunbi-status-and-reservation-to-marathas/ar-AA1LMmVI?cvid=8E7979A87B9E446B96BCD0A5F557FE1C&amp;ocid=hpmsn&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
@@ -452,567 +452,161 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/bhopal-news/mp-government-has-backtracked-on-27-percent-obc-reservation-congress-jitu-patwari-alleges-19922014</t>
+          <t>https://impressivetimes.com/latest/congress-demands-reservation-private-educational-institutions/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/04/maharashtra-congress-urges-cm-fadnavis-to-raise-obc-quota-from-27-to-42-on-telangana-model</t>
+          <t>https://www.devdiscourse.com/article/politics/3614925-obc-protest-ends-as-maharashtra-government-commits-to-reservation-protection</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/03/maratha-community-divided-as-maharashtra-government-issues-gr-on-kunbi-certificates-under-obc-quota</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/obc-fedn-ends-hunger-strike-after-maha-concedes-key-demands/articleshow/123706051.cms</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maratha-quota-agitation-activists-end-protest-as-govt-assures-their-quota-would-remain-untouched-3711729</t>
+          <t>https://m.thewire.in/article/politics/maratha-reservation-row-highlights-differences-within-bjp-led-mahayuti-govt-in-maharashtra/amp</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://impressivetimes.com/latest/congress-demands-reservation-private-educational-institutions/</t>
+          <t>https://www.devdiscourse.com/article/law-order/3615789-maharashtras-balancing-act-maratha-reservation-and-obc-safeguards</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/madhya-pradesh-chhattisgarh/bhopal/mp-government-obc-27-percentage-reservation-case-meeting-in-delhi-13-percent-obc-posts-unhold-demand/2909405</t>
+          <t>https://aninews.in/news/national/general-news/gross-betrayal-breach-of-trust-and-violation-of-social-justice-sravan-dasoju-accuses-centre-ugc-of-failing-to-enforce-bc-reservations20250905225143/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/amp/story/nation/2025/Sep/04/maharashtra-cm-fadnavis-assures-obcs-that-maratha-quota-move-wont-affect-their-reservations</t>
+          <t>https://zeenews.india.com/india/no-intent-to-take-away-reservation-of-one-community-and-giving-to-another-cm-fadnavis-2955596.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.indianewsstream.com/obcs-must-fight-their-own-battle-instead-of-relying-on-any-leader-prakash-ambedkar/</t>
+          <t>https://www.devdiscourse.com/article/law-order/3613986-maharashtras-maratha-reservation-protest-a-tug-of-obc-identity</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/west-bengal-teacher-recruitment-2025-wbssc-announces-35726-teaching-posts-including-17-obc-quota</t>
+          <t>https://www.ptinews.com/story/national/karnataka-reservation-roster-sc-st-obc-quota-at-56-per-cent-general-merit-44-per-cent/2883055</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/karnataka-reservation-roster-sc-st-obc-quota-at-56-per-cent-general-merit-44-per-cent/2883055</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maratha-morcha-no-obc-leader-upset-with-maratha-quota-decision-by-maharashtra-govt-says-bjp-mlc-parinay-fuke-23592332</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/04/if-betrayed-over-maratha-quota-we-will-make-them-bite-the-dust-in-polls-jarange-2</t>
+          <t>https://udayavani.com/karnataka/karnataka-reservation-roster-scst-obc-quota-at-56-per-cent-general-merit-44-per-cent-20250904T024333663Z?lang=en</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/no-intent-to-take-away-reservation-of-one-community-and-giving-to-another-cm-fadnavis-2955596.html</t>
+          <t>https://www.devdiscourse.com/article/headlines/3614421-maharashtra-government-moves-ahead-amid-maratha-reservation-developments</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/have-faith-our-people-in-marathwada-and-western-maharashtra-will-get-reservation-jarange-3709943</t>
+          <t>https://news.careers360.com/west-bengal-teacher-recruitment-2025-wbssc-announces-35726-teaching-posts-including-17-obc-quota</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/03/jarange-expresses-confidence-about-marathas-getting-quota-obc-leaders-unhappy-2</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/03/bom25-mh-quota-bjp-mlc.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/OBC-activists-end-protest-as-govt-assures-their-quota-would-remain-untouched/2884396</t>
+          <t>https://www.socialnews.xyz/?p=6533806</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3614925-obc-protest-ends-as-maharashtra-government-commits-to-reservation-protection</t>
+          <t>https://www.sakshipost.com/news/will-maha-govt-grant-42-pc-reservation-backward-classes-telangana-congress-448562</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/what-is-the-hyderabad-gazette-giving-kunbi-status-and-reservation-to-marathas/ar-AA1LMmVI?cvid=8E7979A87B9E446B96BCD0A5F557FE1C&amp;ocid=hpmsn&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.bhaskarenglish.in/national/news/maratha-reservation-mahayuti-government-obc-organisations-govt-order-chhagan-bhujbal-135835185.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/rajya/maratha-reservation-obc-class-ca-protest-against-the-decision-of-devendra-fadnavis/4123297/</t>
+          <t>https://english.newstrack.com/india-news/hyderabad-gazette-maratha-reservation-538707</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://m-hindi.webdunia.com/madhya-pradesh/political-battle-over-obc-reservation-in-madhya-pradesh-125090500036_1.html</t>
+          <t>https://english.varthabharati.in/index.php/karnataka/karnataka-reservation-roster-scst-obc-quota-at-56-per-cent-general-merit-44-per-cent</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.outlookindia.com/national/jarange-patils-maratha-quota-demand-collides-with-obc-groups-hard-won-27</t>
+          <t>https://kknlive.com/en/political-news/congress-targets-modi-government-ahead-of-bihar-elections/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3615789-maharashtras-balancing-act-maratha-reservation-and-obc-safeguards</t>
+          <t>https://www.hindustantimes.com/india-news/chhagan-bhujbal-says-will-challenge-gr-on-maratha-quota-in-court-101756910519244.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3613986-maharashtras-maratha-reservation-protest-a-tug-of-obc-identity</t>
+          <t>https://www.lokmattimes.com/national/chhagan-bhujbal-boycotts-cabinet-meeting-a-day-after-govt-decides-to-provide-kunbi-status-to-marathas/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/bhopal/politics-on-obc-reservation-in-mp-minister-krishna-gaur-targeted-congress-1379465.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/maratha-reservation-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%93%E0%A4%82-%E0%A4%95-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%A6%E0%A5%87%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A5%87-%E0%A4%AC-%E0%A4%A6-%E0%A4%93%E0%A4%AC-%E0%A4%B8-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%A4%E0%A4%B0%E0%A4%B9-%E0%A4%B8%E0%A5%87-%E0%A4%A8-%E0%A4%B0-%E0%A4%9C-%E0%A4%B9%E0%A5%88/vi-AA1LUMuz</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/story/national/obcs-will-take-to-streets-activist-on-govt-s-maratha-quota-decision/2880855</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/maratha-quota-gr-row-obcs-will-not-be-impacted-bhujbal-will-be-pacified-says-cm-devendra-fadnavis-video</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/maratha-aarakshan-prakash-ambedkar-said-maratha-reservation-cannot-be-given-from-obc-quota-1378735.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/bachchu-kadu-criticism-bjp-maratha-obc-reservation-bhandara-pp82</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>https://gujarati.abplive.com/short-videos/news/gujarat-bjp-mla-s-big-statement-on-obc-reservation-issue-rich-caste-takes-away-our-share-of-reservation-954139</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/maharashtra/maratha-obc-reservation-row-heats-up-power-tussle-inside-ncp-devgiri-bungalow-becomes-political-hotspot-bbj88</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-mumbai-pune-rain-news-maratha-vs-obc-reservation-crime-accident-updates-local-headlines-9219984</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/maratha-leaders-fighting-over-obc-reservation-keep-a-comfortable-silence-on-government-contract-jobs-sd67</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/obc-reservation-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8-%E0%A4%B2%E0%A4%A2-%E0%A4%88%E0%A4%B8-%E0%A4%A0-%E0%A4%B5%E0%A4%95-%E0%A4%B2-%E0%A4%8F%E0%A4%95%E0%A4%B5%E0%A4%9F%E0%A4%B2%E0%A5%87-%E0%A4%93%E0%A4%AC-%E0%A4%B8-%E0%A4%AE%E0%A4%B9-%E0%A4%B8%E0%A4%82%E0%A4%98-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A5%88%E0%A4%A0%E0%A4%95-%E0%A4%A4-%E0%A4%AA-%E0%A4%9A-%E0%A4%A0%E0%A4%B0-%E0%A4%B5-%E0%A4%AE%E0%A4%82%E0%A4%9C%E0%A5%82%E0%A4%B0/ar-AA1LXKUh</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nagpur-lawyers-unite-for-legal-battle-obc-mahasangh-meeting-passes-five-resolutions-as80</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/chhagan-bhujbal-to-move-court-against-devendra-fadnavis-government-maratha-reservation-gr-appeals-obcs-to-halt-protests-vvg94</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-government-big-decision-forms-separate-cabinet-subcommittee-for-obc-reservation-policy-msr87</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/mumbai/maratha-reservation-gr-eknath-shinde-obc-statement-manoj-jarange-patil-obc-jap93</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/obc-reservation-news-maratha-vs-obc-%E0%A4%85%E0%A4%82%E0%A4%A4%E0%A4%B0%E0%A4%B5-%E0%A4%B2-%E0%A4%B8%E0%A4%B0-%E0%A4%9F-%E0%A4%A4-obc-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%9A%E0%A4%82-%E0%A4%89%E0%A4%AA-%E0%A4%B7%E0%A4%A3-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A4%A3%E0%A4%82-n18v/vi-AA1LQo9C?ocid=hpmsn</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/mumbai/maratha-reservation-protest-obc-anger-bjp-political-impact-mahayuti-bmc-mahavikas-aghadi-jap93</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/obc-reservation-%E0%A4%93%E0%A4%AC-%E0%A4%B8-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%85%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%B9-%E0%A4%8A-%E0%A4%A6%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%B8%E0%A4%AE-%E0%A4%A4-%E0%A4%97%E0%A4%A0-%E0%A4%A4-%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0%E0%A4%A3%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AA%E0%A4%82%E0%A4%95%E0%A4%9C-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%A1%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%97%E0%A5%8D%E0%A4%B5-%E0%A4%B9/ar-AA1LV2kW</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/maharashtra/manoj-jarange-claims-maratha-community-officially-in-obc-category-chhagan-bhujbal-warns-of-court-action-eknath-shinde-dismisses-blanket-reservation-maharashtra-political-conflict-om0906</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>https://marathi.ndtv.com/india/maratha-reservation-maratha-morcha-manoj-jarange-live-update-obc-leader-oppose-gst-council-meeting-gst-slab-9213266</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chhagan-bhujbal-if-majatha-community-get-obc-reservation-will-make-adverse-effect-on-obc-jobs-sd67</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>https://www.anandabazar.com/education-career/ssc-releases-list-of-new-vacancies-ahead-of-17-percent-obc-reservation-recruitment-exam-dgtl/cid/1630953</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/maratha-reservation-news-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%9A-%E0%A4%A4-gr-%E0%A4%B0%E0%A4%A6%E0%A5%8D%E0%A4%A6-%E0%A4%95%E0%A4%B0-dharashiv-%E0%A4%AF%E0%A5%87%E0%A4%A5%E0%A5%87-obc-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%8F%E0%A4%95%E0%A4%B5%E0%A4%9F%E0%A4%B2/vi-AA1LSeMl?ocid=hpmsn</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/maharashtra/gulabrao-patil-informed-that-a-cabinet-sub-committee-has-been-formed-for-the-obc-community/918089/</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/mumbai/marathas-or-obcs-marathas-or-obcs-whose-support-everyone-is-in-confusion-ar84</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/obc-mahasangh-protest-suspended-devendra-fadnavis-atul-save-mediation-demands-rm82</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/video/maratha-andolan-laxman-hake-obc-reservation-opposition-mumbai-nrs96</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-manoj-jarange-kunbi-certificate-maratha-obc-reservation-controversy-mm76-rc70</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>https://news18marathi.com/maharashtra/eknath-shinde-shocking-reveal-on-chhagan-bhujbal-maratha-reservation-obc-reservation-row-1473342.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/prashasan/maharashtra-cabinet-aproved-obc-sub-committee-these-ministers-included-big-responsibility-chhagan-bhujbal-chandrashekhar-bawankule-aau85</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/video/obc-demands-babanrao-taywade-parinay-phuke-reaction-scholarship-housing-farmers-compensation-reservation-om0906</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>https://news18marathi.com/maharashtra/obc-leaders-in-action-mode-after-maharashtra-government-issue-gr-regarding-maratha-reservation-check-update-here-1472153.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>https://www.prajavani.net/news/india-news/maratha-reservation-obc-leader-opposes-3508448</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/maharashtra/obc-agitation-antarwali-sarati-protest-maratha-reservation-gr-chhagan-bhujbal-appeal-ymk86</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/marathwada/obc-activists-vow-hunger-strike-until-gr-is-cancelled-vadigodri-pjp78</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/video/devendra-fadnavis-assures-no-injustice-to-obcs-amid-maratha-quota-gr-row-om0906</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/video/chhagan-bhujbal-opposes-maratha-inclusion-in-obc-quota-hyderabad-gazetteer-kunbi-certificate-court-warning-om0906</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/video/chhagan-bhujbal-obc-leaders-crucial-meeting-in-mumbai-after-maratha-reservation-ordinance-om0906</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/video/obc-community-protests-maratha-reservation-gr-in-jalna-tears-copy-tramples-under-feet-over-government-order-controversy-om0906</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/mahamumbai/thane/shahapur-obc-kalyan-obcs-agitation-for-reservation-in-shahapur-postponed/918562/</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-cm-devendra-fadnavis-clarifies-hyderabad-gazette-gr-for-maratha-reservation-and-chaggan-bhujbal-unhappiness-issue-snk89</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/editorial/agralekha/fadnavis-government-issued-gr-on-maratha-reservation-and-obc-leaders-opposed/918160/</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/maharashtra/obc-community-tears-up-copy-of-gr-alleging-that-maratha-reservation-is-being-given-through-obc-andolan/918021/</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-5th-september-2025-marathi-live-devendra-fadnavis-obc-maratha-reservation-ganeshotsav-mumbai-goa-highway-traffic/liveblog/123709822.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/video/sunil-tatkare-reaction-to-chhagan-bhujbal-remarks-says-obc-reservation-safe-maratha-quota-decision-taken-after-discussion-om0906</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/parbhani/obc-activist-in-parbhani-warn-devendra-fadnavis-government-over-maratha-reservation-gr/videoshow/123676162.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/videos/obc-protest-maratha-reservation-gr-manoj-jarange-patil-dharashiv-dharna-kr13</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/amp/videos/maratha-reservation-demands-accepted-obc-community-upset-maharashtra-government-forms-separate-obc-cabinet-sub-committee-hyderabad-aundh-gazetteer-gr-kr13</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/video/rift-in-ruling-alliance-chhagan-bhujbal-angry-over-maratha-reservation-radhakrishna-vikhe-patil-hits-back-om0906</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>https://www.tv9marathi.com/videos/short-videos/obc-community-warned-government-demanding-cancellation-of-gr-regarding-maratha-reservation</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/jalgaon/maratha-reservation-give-reservation-to-marathas-without-disrupting-obc-reservation-obc-communitys-call-ar84</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/if-reservation-is-given-to-marathas-from-obcs-both-will-suffer-chhagan-bhujbal-explained-how-marathas-will-suffer-aau85</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/local/maharashtra/obc-reservation-revenue-minister-warns-against-disrupting-social-harmony-4250708</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>https://www.sakshipost.com/news/will-maha-govt-grant-42-pc-reservation-backward-classes-telangana-congress-448562</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>https://hindi.newsdanka.com/politics/sanjay-raut-chhagan-bhujbal-obc-reservation-resign-2025/113995/</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/india-news/chhagan-bhujbal-says-will-challenge-gr-on-maratha-quota-in-court-101756910519244.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/law-order/3615625-maratha-quota-movement-a-call-for-justice-and-inclusion</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>https://www.dailyexcelsior.com/jarange-exults-bhujbal-sulks-minister-skips-cabinet-meet-says-will-challenge-maratha-quota-gr/</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/video/baramati-police-deny-permission-for-obc-morcha-led-by-laxman-hake-watch-video-latest-news-pvm91</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bhujbal-skips-cabinet-meet-says-will-challenge-gr-in-court-101756926793110.html</t>
         </is>
       </c>
     </row>

--- a/Output/OBC Andolan/extracted_links_OBC Andolan_failed_links.xlsx
+++ b/Output/OBC Andolan/extracted_links_OBC Andolan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,105 +466,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/obc-fedn-ends-hunger-strike-after-maha-concedes-key-demands/articleshow/123706051.cms</t>
+          <t>https://www.devdiscourse.com/article/law-order/3615789-maharashtras-balancing-act-maratha-reservation-and-obc-safeguards</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/politics/maratha-reservation-row-highlights-differences-within-bjp-led-mahayuti-govt-in-maharashtra/amp</t>
+          <t>https://aninews.in/news/national/general-news/gross-betrayal-breach-of-trust-and-violation-of-social-justice-sravan-dasoju-accuses-centre-ugc-of-failing-to-enforce-bc-reservations20250905225143/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3615789-maharashtras-balancing-act-maratha-reservation-and-obc-safeguards</t>
+          <t>https://zeenews.india.com/india/no-intent-to-take-away-reservation-of-one-community-and-giving-to-another-cm-fadnavis-2955596.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/gross-betrayal-breach-of-trust-and-violation-of-social-justice-sravan-dasoju-accuses-centre-ugc-of-failing-to-enforce-bc-reservations20250905225143/</t>
+          <t>https://www.devdiscourse.com/article/law-order/3613986-maharashtras-maratha-reservation-protest-a-tug-of-obc-identity</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/no-intent-to-take-away-reservation-of-one-community-and-giving-to-another-cm-fadnavis-2955596.html</t>
+          <t>https://www.indianewsstream.com/obcs-must-fight-their-own-battle-instead-of-relying-on-any-leader-prakash-ambedkar/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3613986-maharashtras-maratha-reservation-protest-a-tug-of-obc-identity</t>
+          <t>https://www.ptinews.com/story/national/karnataka-reservation-roster-sc-st-obc-quota-at-56-per-cent-general-merit-44-per-cent/2883055</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/karnataka-reservation-roster-sc-st-obc-quota-at-56-per-cent-general-merit-44-per-cent/2883055</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maratha-morcha-no-obc-leader-upset-with-maratha-quota-decision-by-maharashtra-govt-says-bjp-mlc-parinay-fuke-23592332</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maratha-morcha-no-obc-leader-upset-with-maratha-quota-decision-by-maharashtra-govt-says-bjp-mlc-parinay-fuke-23592332</t>
+          <t>https://udayavani.com/karnataka/karnataka-reservation-roster-scst-obc-quota-at-56-per-cent-general-merit-44-per-cent-20250904T024333663Z?lang=en</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://udayavani.com/karnataka/karnataka-reservation-roster-scst-obc-quota-at-56-per-cent-general-merit-44-per-cent-20250904T024333663Z?lang=en</t>
+          <t>https://www.devdiscourse.com/article/headlines/3614421-maharashtra-government-moves-ahead-amid-maratha-reservation-developments</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3614421-maharashtra-government-moves-ahead-amid-maratha-reservation-developments</t>
+          <t>https://www.theweek.in/news/india/2025/09/03/will-take-to-streets-as-jarange-s-hunger-strike-ends-maharashtra-govt-now-faces-ob-cs-ire.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/west-bengal-teacher-recruitment-2025-wbssc-announces-35726-teaching-posts-including-17-obc-quota</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/03/bes17-mh-quota-obc-protest.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/03/bom25-mh-quota-bjp-mlc.html</t>
+          <t>https://www.socialnews.xyz/?p=6533806</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6533806</t>
+          <t>https://www.sakshipost.com/news/will-maha-govt-grant-42-pc-reservation-backward-classes-telangana-congress-448562</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/will-maha-govt-grant-42-pc-reservation-backward-classes-telangana-congress-448562</t>
+          <t>https://www.bhaskarenglish.in/national/news/maratha-reservation-mahayuti-government-obc-organisations-govt-order-chhagan-bhujbal-135835185.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/maratha-reservation-mahayuti-government-obc-organisations-govt-order-chhagan-bhujbal-135835185.html</t>
+          <t>https://www.thehawk.in/news/india/bhujbal-urges-obc-leaders-to-halt-protests-over-maratha-kunbi-status-mulls-legal-options</t>
         </is>
       </c>
     </row>
@@ -578,33 +578,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/index.php/karnataka/karnataka-reservation-roster-scst-obc-quota-at-56-per-cent-general-merit-44-per-cent</t>
+          <t>https://kknlive.com/en/political-news/congress-targets-modi-government-ahead-of-bihar-elections/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://kknlive.com/en/political-news/congress-targets-modi-government-ahead-of-bihar-elections/</t>
+          <t>https://www.hindustantimes.com/india-news/chhagan-bhujbal-says-will-challenge-gr-on-maratha-quota-in-court-101756910519244.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/chhagan-bhujbal-says-will-challenge-gr-on-maratha-quota-in-court-101756910519244.html</t>
+          <t>https://www.devdiscourse.com/article/law-order/3615625-maratha-quota-movement-a-call-for-justice-and-inclusion</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/national/chhagan-bhujbal-boycotts-cabinet-meeting-a-day-after-govt-decides-to-provide-kunbi-status-to-marathas/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
         <is>
           <t>https://www.hindustantimes.com/cities/mumbai-news/bhujbal-skips-cabinet-meet-says-will-challenge-gr-in-court-101756926793110.html</t>
         </is>

--- a/Output/OBC Andolan/extracted_links_OBC Andolan_failed_links.xlsx
+++ b/Output/OBC Andolan/extracted_links_OBC Andolan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,138 +466,124 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3615789-maharashtras-balancing-act-maratha-reservation-and-obc-safeguards</t>
+          <t>https://aninews.in/news/national/general-news/gross-betrayal-breach-of-trust-and-violation-of-social-justice-sravan-dasoju-accuses-centre-ugc-of-failing-to-enforce-bc-reservations20250905225143/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/gross-betrayal-breach-of-trust-and-violation-of-social-justice-sravan-dasoju-accuses-centre-ugc-of-failing-to-enforce-bc-reservations20250905225143/</t>
+          <t>https://zeenews.india.com/india/no-intent-to-take-away-reservation-of-one-community-and-giving-to-another-cm-fadnavis-2955596.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/no-intent-to-take-away-reservation-of-one-community-and-giving-to-another-cm-fadnavis-2955596.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maratha-morcha-no-obc-leader-upset-with-maratha-quota-decision-by-maharashtra-govt-says-bjp-mlc-parinay-fuke-23592332</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3613986-maharashtras-maratha-reservation-protest-a-tug-of-obc-identity</t>
+          <t>https://www.indianewsstream.com/obcs-must-fight-their-own-battle-instead-of-relying-on-any-leader-prakash-ambedkar/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.indianewsstream.com/obcs-must-fight-their-own-battle-instead-of-relying-on-any-leader-prakash-ambedkar/</t>
+          <t>https://www.ptinews.com/story/national/karnataka-reservation-roster-sc-st-obc-quota-at-56-per-cent-general-merit-44-per-cent/2883055</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/karnataka-reservation-roster-sc-st-obc-quota-at-56-per-cent-general-merit-44-per-cent/2883055</t>
+          <t>https://www.devdiscourse.com/article/headlines/3614421-maharashtra-government-moves-ahead-amid-maratha-reservation-developments</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maratha-morcha-no-obc-leader-upset-with-maratha-quota-decision-by-maharashtra-govt-says-bjp-mlc-parinay-fuke-23592332</t>
+          <t>https://udayavani.com/karnataka/karnataka-reservation-roster-scst-obc-quota-at-56-per-cent-general-merit-44-per-cent-20250904T024333663Z?lang=en</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://udayavani.com/karnataka/karnataka-reservation-roster-scst-obc-quota-at-56-per-cent-general-merit-44-per-cent-20250904T024333663Z?lang=en</t>
+          <t>https://www.devdiscourse.com/article/law-order/3613654-maratha-quota-decision-a-balancing-act</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3614421-maharashtra-government-moves-ahead-amid-maratha-reservation-developments</t>
+          <t>https://news.careers360.com/west-bengal-teacher-recruitment-2025-wbssc-announces-35726-teaching-posts-including-17-obc-quota</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/india/2025/09/03/will-take-to-streets-as-jarange-s-hunger-strike-ends-maharashtra-govt-now-faces-ob-cs-ire.html</t>
+          <t>https://www.sakshipost.com/news/will-maha-govt-grant-42-pc-reservation-backward-classes-telangana-congress-448562</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/03/bes17-mh-quota-obc-protest.html</t>
+          <t>https://www.bhaskarenglish.in/local/mp/news/obc-reservation-case-supreme-court-hearing-13-percent-posts-madhya-pradesh-135843416.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6533806</t>
+          <t>https://www.bhaskarenglish.in/national/news/maratha-reservation-mahayuti-government-obc-organisations-govt-order-chhagan-bhujbal-135835185.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/will-maha-govt-grant-42-pc-reservation-backward-classes-telangana-congress-448562</t>
+          <t>https://english.newstrack.com/india-news/hyderabad-gazette-maratha-reservation-538707</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/maratha-reservation-mahayuti-government-obc-organisations-govt-order-chhagan-bhujbal-135835185.html</t>
+          <t>https://kknlive.com/en/political-news/congress-targets-modi-government-ahead-of-bihar-elections/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/bhujbal-urges-obc-leaders-to-halt-protests-over-maratha-kunbi-status-mulls-legal-options</t>
+          <t>https://www.hindustantimes.com/india-news/chhagan-bhujbal-says-will-challenge-gr-on-maratha-quota-in-court-101756910519244.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://english.newstrack.com/india-news/hyderabad-gazette-maratha-reservation-538707</t>
+          <t>https://www.msn.com/en-in/news/India/jarange-exults-bhujbal-sulks-minister-skips-cabinet-meet-says-will-challenge-maratha-quota-gr/ar-AA1LNGX4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://kknlive.com/en/political-news/congress-targets-modi-government-ahead-of-bihar-elections/</t>
+          <t>https://www.lokmattimes.com/national/chhagan-bhujbal-boycotts-cabinet-meeting-a-day-after-govt-decides-to-provide-kunbi-status-to-marathas/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/india-news/chhagan-bhujbal-says-will-challenge-gr-on-maratha-quota-in-court-101756910519244.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/law-order/3615625-maratha-quota-movement-a-call-for-justice-and-inclusion</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
         <is>
           <t>https://www.hindustantimes.com/cities/mumbai-news/bhujbal-skips-cabinet-meet-says-will-challenge-gr-in-court-101756926793110.html</t>
         </is>
